--- a/schemas/student-import-template.xlsx
+++ b/schemas/student-import-template.xlsx
@@ -4,7 +4,6 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Students_Template" sheetId="1" r:id="rId1"/>
-    <sheet name="Readme" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -33,8 +32,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -398,256 +399,202 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S2"/>
-  <cols>
-    <col min="1" max="1" width="18.83203125" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="18.83203125" customWidth="1"/>
-    <col min="5" max="5" width="18.83203125" customWidth="1"/>
-    <col min="6" max="6" width="18.83203125" customWidth="1"/>
-    <col min="7" max="7" width="18.83203125" customWidth="1"/>
-    <col min="8" max="8" width="18.83203125" customWidth="1"/>
-    <col min="9" max="9" width="18.83203125" customWidth="1"/>
-    <col min="10" max="10" width="18.83203125" customWidth="1"/>
-    <col min="11" max="11" width="18.83203125" customWidth="1"/>
-    <col min="12" max="12" width="18.83203125" customWidth="1"/>
-    <col min="13" max="13" width="18.83203125" customWidth="1"/>
-    <col min="14" max="14" width="24.83203125" customWidth="1"/>
-    <col min="15" max="15" width="18.83203125" customWidth="1"/>
-    <col min="16" max="16" width="18.83203125" customWidth="1"/>
-    <col min="17" max="17" width="24.83203125" customWidth="1"/>
-    <col min="18" max="18" width="18.83203125" customWidth="1"/>
-    <col min="19" max="19" width="18.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:BK1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>studentId</v>
+        <v>student-photo</v>
       </c>
       <c r="B1" t="str">
-        <v>fullName</v>
+        <v>full-name-student</v>
       </c>
       <c r="C1" t="str">
-        <v>englishName</v>
+        <v>english-name</v>
       </c>
       <c r="D1" t="str">
+        <v>gender</v>
+      </c>
+      <c r="E1" t="str">
+        <v>member-since</v>
+      </c>
+      <c r="F1" t="str">
+        <v>student-number</v>
+      </c>
+      <c r="G1" t="str">
+        <v>eagles-id</v>
+      </c>
+      <c r="H1" t="str">
+        <v>password</v>
+      </c>
+      <c r="I1" t="str">
+        <v>parents-id</v>
+      </c>
+      <c r="J1" t="str">
+        <v>student-phone</v>
+      </c>
+      <c r="K1" t="str">
+        <v>student-email</v>
+      </c>
+      <c r="L1" t="str">
+        <v>class-level</v>
+      </c>
+      <c r="M1" t="str">
+        <v>exercise-points</v>
+      </c>
+      <c r="N1" t="str">
+        <v>hobbies</v>
+      </c>
+      <c r="O1" t="str">
         <v>dob</v>
       </c>
-      <c r="E1" t="str">
-        <v>studentEmail</v>
-      </c>
-      <c r="F1" t="str">
-        <v>studentPhone</v>
-      </c>
-      <c r="G1" t="str">
-        <v>schoolName</v>
-      </c>
-      <c r="H1" t="str">
-        <v>currentGrade</v>
-      </c>
-      <c r="I1" t="str">
-        <v>streetAddress</v>
-      </c>
-      <c r="J1" t="str">
-        <v>wardDistrict</v>
-      </c>
-      <c r="K1" t="str">
+      <c r="P1" t="str">
+        <v>birth-order</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>number-of-siblings-male</v>
+      </c>
+      <c r="R1" t="str">
+        <v>number-of-siblings-female</v>
+      </c>
+      <c r="S1" t="str">
+        <v>ethnicity</v>
+      </c>
+      <c r="T1" t="str">
+        <v>languages-home</v>
+      </c>
+      <c r="U1" t="str">
+        <v>describe-other-language</v>
+      </c>
+      <c r="V1" t="str">
+        <v>student-school</v>
+      </c>
+      <c r="W1" t="str">
+        <v>student-current-grade</v>
+      </c>
+      <c r="X1" t="str">
+        <v>full-name_mother</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>email-ma</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>ma-is-homework-proctor</v>
+      </c>
+      <c r="AA1" t="str">
+        <v>mothers-phone</v>
+      </c>
+      <c r="AB1" t="str">
+        <v>emergency-contact-mother</v>
+      </c>
+      <c r="AC1" t="str">
+        <v>zalo-im-id-mother</v>
+      </c>
+      <c r="AD1" t="str">
+        <v>full-name_father</v>
+      </c>
+      <c r="AE1" t="str">
+        <v>email-ba</v>
+      </c>
+      <c r="AF1" t="str">
+        <v>ba-is-homework-proctor</v>
+      </c>
+      <c r="AG1" t="str">
+        <v>fathers-phone</v>
+      </c>
+      <c r="AH1" t="str">
+        <v>emergency-contact-father</v>
+      </c>
+      <c r="AI1" t="str">
+        <v>zalo-im-id-ba</v>
+      </c>
+      <c r="AJ1" t="str">
+        <v>street-address</v>
+      </c>
+      <c r="AK1" t="str">
+        <v>new-address</v>
+      </c>
+      <c r="AL1" t="str">
+        <v>ward-district</v>
+      </c>
+      <c r="AM1" t="str">
         <v>city</v>
       </c>
-      <c r="L1" t="str">
-        <v>motherName</v>
-      </c>
-      <c r="M1" t="str">
-        <v>motherPhone</v>
-      </c>
-      <c r="N1" t="str">
-        <v>motherEmergencyContact</v>
-      </c>
-      <c r="O1" t="str">
-        <v>fatherName</v>
-      </c>
-      <c r="P1" t="str">
-        <v>fatherPhone</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>fatherEmergencyContact</v>
-      </c>
-      <c r="R1" t="str">
-        <v>photoUrl</v>
-      </c>
-      <c r="S1" t="str">
-        <v>email</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>S0001</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Jane Student</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Jane</v>
-      </c>
-      <c r="D2" t="str">
-        <v>2014-10-01</v>
-      </c>
-      <c r="E2" t="str">
-        <v>jane.parent@example.com</v>
-      </c>
-      <c r="F2" t="str">
-        <v>0900111222</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Eagles School</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Grade 5</v>
-      </c>
-      <c r="I2" t="str">
-        <v>123 Main St</v>
-      </c>
-      <c r="J2" t="str">
-        <v>District 1</v>
-      </c>
-      <c r="K2" t="str">
-        <v>HCMC</v>
-      </c>
-      <c r="L2" t="str">
-        <v>Maria Student</v>
-      </c>
-      <c r="M2" t="str">
-        <v>0900111222</v>
-      </c>
-      <c r="N2" t="str">
-        <v>0900111222</v>
-      </c>
-      <c r="O2" t="str">
-        <v>John Student</v>
-      </c>
-      <c r="P2" t="str">
-        <v>0900555666</v>
-      </c>
-      <c r="Q2" t="str">
-        <v>0900555666</v>
-      </c>
-      <c r="R2" t="str">
-        <v>https://example.com/student-photo.jpg</v>
-      </c>
-      <c r="S2" t="str">
-        <v>jane.parent@example.com</v>
+      <c r="AN1" t="str">
+        <v>post-code</v>
+      </c>
+      <c r="AO1" t="str">
+        <v>wear-glasses</v>
+      </c>
+      <c r="AP1" t="str">
+        <v>last-eye-exam</v>
+      </c>
+      <c r="AQ1" t="str">
+        <v>date-last-eye-exam</v>
+      </c>
+      <c r="AR1" t="str">
+        <v>prescription-medicine</v>
+      </c>
+      <c r="AS1" t="str">
+        <v>explain-list-rx-meds</v>
+      </c>
+      <c r="AT1" t="str">
+        <v>learning-disorders</v>
+      </c>
+      <c r="AU1" t="str">
+        <v>explain-ld-bd</v>
+      </c>
+      <c r="AV1" t="str">
+        <v>drug-allergies-list</v>
+      </c>
+      <c r="AW1" t="str">
+        <v>food-environmental-allergies-list</v>
+      </c>
+      <c r="AX1" t="str">
+        <v>childhood-vaccines-utd</v>
+      </c>
+      <c r="AY1" t="str">
+        <v>childhood-vaccine-record</v>
+      </c>
+      <c r="AZ1" t="str">
+        <v>covid-19-positive-or-had-it</v>
+      </c>
+      <c r="BA1" t="str">
+        <v>date-negative-after-infections</v>
+      </c>
+      <c r="BB1" t="str">
+        <v>had-covid-shot-already</v>
+      </c>
+      <c r="BC1" t="str">
+        <v>covid-19-vaccine-utd</v>
+      </c>
+      <c r="BD1" t="str">
+        <v>most-recent-covid-shot</v>
+      </c>
+      <c r="BE1" t="str">
+        <v>comments</v>
+      </c>
+      <c r="BF1" t="str">
+        <v>check-each-covid-injection-student-has-had</v>
+      </c>
+      <c r="BG1" t="str">
+        <v>covid-vaccine-records</v>
+      </c>
+      <c r="BH1" t="str">
+        <v>fever-medicine</v>
+      </c>
+      <c r="BI1" t="str">
+        <v>dau-trang-duoc</v>
+      </c>
+      <c r="BJ1" t="str">
+        <v>signature</v>
+      </c>
+      <c r="BK1" t="str">
+        <v>email-form-sig</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S2"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B14"/>
-  <cols>
-    <col min="1" max="1" width="32.83203125" customWidth="1"/>
-    <col min="2" max="2" width="90.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Student Import Template</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Required: studentId (must be unique per student).</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Primary accepted formats: .xlsx, .xls, .csv, .tsv.</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Do not duplicate studentId values in one upload file.</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Column notes:</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>studentId</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Required unique identifier used by admin import.</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>fullName</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Student full name (recommended).</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>currentGrade</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Level/Grade for filtering and class grouping.</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>motherEmergencyContact</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Used for family search by emergency phone.</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>fatherEmergencyContact</v>
-      </c>
-      <c r="B12" t="str">
-        <v>Used for family search by emergency phone.</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>photoUrl</v>
-      </c>
-      <c r="B13" t="str">
-        <v>Optional URL or data URI used in PDF report card image.</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>email</v>
-      </c>
-      <c r="B14" t="str">
-        <v>Fallback student email if studentEmail is empty.</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:BK1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/schemas/student-import-template.xlsx
+++ b/schemas/student-import-template.xlsx
@@ -403,43 +403,43 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>student-photo</v>
+        <v>studentPhoto</v>
       </c>
       <c r="B1" t="str">
-        <v>full-name-student</v>
+        <v>fullNameStudent</v>
       </c>
       <c r="C1" t="str">
-        <v>english-name</v>
+        <v>englishName</v>
       </c>
       <c r="D1" t="str">
         <v>gender</v>
       </c>
       <c r="E1" t="str">
-        <v>member-since</v>
+        <v>memberSince</v>
       </c>
       <c r="F1" t="str">
-        <v>student-number</v>
+        <v>studentNumber</v>
       </c>
       <c r="G1" t="str">
-        <v>eagles-id</v>
+        <v>eaglesId</v>
       </c>
       <c r="H1" t="str">
         <v>password</v>
       </c>
       <c r="I1" t="str">
-        <v>parents-id</v>
+        <v>parentsId</v>
       </c>
       <c r="J1" t="str">
-        <v>student-phone</v>
+        <v>studentPhone</v>
       </c>
       <c r="K1" t="str">
-        <v>student-email</v>
+        <v>studentEmail</v>
       </c>
       <c r="L1" t="str">
-        <v>class-level</v>
+        <v>classLevel</v>
       </c>
       <c r="M1" t="str">
-        <v>exercise-points</v>
+        <v>exercisePoints</v>
       </c>
       <c r="N1" t="str">
         <v>hobbies</v>
@@ -448,148 +448,148 @@
         <v>dob</v>
       </c>
       <c r="P1" t="str">
-        <v>birth-order</v>
+        <v>birthOrder</v>
       </c>
       <c r="Q1" t="str">
-        <v>number-of-siblings-male</v>
+        <v>numberOfSiblingsMale</v>
       </c>
       <c r="R1" t="str">
-        <v>number-of-siblings-female</v>
+        <v>numberOfSiblingsFemale</v>
       </c>
       <c r="S1" t="str">
         <v>ethnicity</v>
       </c>
       <c r="T1" t="str">
-        <v>languages-home</v>
+        <v>languagesHome</v>
       </c>
       <c r="U1" t="str">
-        <v>describe-other-language</v>
+        <v>describeOtherLanguage</v>
       </c>
       <c r="V1" t="str">
-        <v>student-school</v>
+        <v>studentSchool</v>
       </c>
       <c r="W1" t="str">
-        <v>student-current-grade</v>
+        <v>studentCurrentGrade</v>
       </c>
       <c r="X1" t="str">
-        <v>full-name_mother</v>
+        <v>fullNameMother</v>
       </c>
       <c r="Y1" t="str">
-        <v>email-ma</v>
+        <v>emailMa</v>
       </c>
       <c r="Z1" t="str">
-        <v>ma-is-homework-proctor</v>
+        <v>maIsHomeworkProctor</v>
       </c>
       <c r="AA1" t="str">
-        <v>mothers-phone</v>
+        <v>mothersPhone</v>
       </c>
       <c r="AB1" t="str">
-        <v>emergency-contact-mother</v>
+        <v>emergencyContactMother</v>
       </c>
       <c r="AC1" t="str">
-        <v>zalo-im-id-mother</v>
+        <v>zaloImIdMother</v>
       </c>
       <c r="AD1" t="str">
-        <v>full-name_father</v>
+        <v>fullNameFather</v>
       </c>
       <c r="AE1" t="str">
-        <v>email-ba</v>
+        <v>emailBa</v>
       </c>
       <c r="AF1" t="str">
-        <v>ba-is-homework-proctor</v>
+        <v>baIsHomeworkProctor</v>
       </c>
       <c r="AG1" t="str">
-        <v>fathers-phone</v>
+        <v>fathersPhone</v>
       </c>
       <c r="AH1" t="str">
-        <v>emergency-contact-father</v>
+        <v>emergencyContactFather</v>
       </c>
       <c r="AI1" t="str">
-        <v>zalo-im-id-ba</v>
+        <v>zaloImIdBa</v>
       </c>
       <c r="AJ1" t="str">
-        <v>street-address</v>
+        <v>streetAddress</v>
       </c>
       <c r="AK1" t="str">
-        <v>new-address</v>
+        <v>newAddress</v>
       </c>
       <c r="AL1" t="str">
-        <v>ward-district</v>
+        <v>wardDistrict</v>
       </c>
       <c r="AM1" t="str">
         <v>city</v>
       </c>
       <c r="AN1" t="str">
-        <v>post-code</v>
+        <v>postCode</v>
       </c>
       <c r="AO1" t="str">
-        <v>wear-glasses</v>
+        <v>wearGlasses</v>
       </c>
       <c r="AP1" t="str">
-        <v>last-eye-exam</v>
+        <v>lastEyeExam</v>
       </c>
       <c r="AQ1" t="str">
-        <v>date-last-eye-exam</v>
+        <v>dateLastEyeExam</v>
       </c>
       <c r="AR1" t="str">
-        <v>prescription-medicine</v>
+        <v>prescriptionMedicine</v>
       </c>
       <c r="AS1" t="str">
-        <v>explain-list-rx-meds</v>
+        <v>explainListRxMeds</v>
       </c>
       <c r="AT1" t="str">
-        <v>learning-disorders</v>
+        <v>learningDisorders</v>
       </c>
       <c r="AU1" t="str">
-        <v>explain-ld-bd</v>
+        <v>explainLdBd</v>
       </c>
       <c r="AV1" t="str">
-        <v>drug-allergies-list</v>
+        <v>drugAllergiesList</v>
       </c>
       <c r="AW1" t="str">
-        <v>food-environmental-allergies-list</v>
+        <v>foodEnvironmentalAllergiesList</v>
       </c>
       <c r="AX1" t="str">
-        <v>childhood-vaccines-utd</v>
+        <v>childhoodVaccinesUtd</v>
       </c>
       <c r="AY1" t="str">
-        <v>childhood-vaccine-record</v>
+        <v>childhoodVaccineRecord</v>
       </c>
       <c r="AZ1" t="str">
-        <v>covid-19-positive-or-had-it</v>
+        <v>covid19PositiveOrHadIt</v>
       </c>
       <c r="BA1" t="str">
-        <v>date-negative-after-infections</v>
+        <v>dateNegativeAfterInfections</v>
       </c>
       <c r="BB1" t="str">
-        <v>had-covid-shot-already</v>
+        <v>hadCovidShotAlready</v>
       </c>
       <c r="BC1" t="str">
-        <v>covid-19-vaccine-utd</v>
+        <v>covid19VaccineUtd</v>
       </c>
       <c r="BD1" t="str">
-        <v>most-recent-covid-shot</v>
+        <v>mostRecentCovidShot</v>
       </c>
       <c r="BE1" t="str">
         <v>comments</v>
       </c>
       <c r="BF1" t="str">
-        <v>check-each-covid-injection-student-has-had</v>
+        <v>checkEachCovidInjectionStudentHasHad</v>
       </c>
       <c r="BG1" t="str">
-        <v>covid-vaccine-records</v>
+        <v>covidVaccineRecords</v>
       </c>
       <c r="BH1" t="str">
-        <v>fever-medicine</v>
+        <v>feverMedicine</v>
       </c>
       <c r="BI1" t="str">
-        <v>dau-trang-duoc</v>
+        <v>dauTrangDuoc</v>
       </c>
       <c r="BJ1" t="str">
         <v>signature</v>
       </c>
       <c r="BK1" t="str">
-        <v>email-form-sig</v>
+        <v>emailFormSig</v>
       </c>
     </row>
   </sheetData>
